--- a/artfynd/A 41202-2024 artfynd.xlsx
+++ b/artfynd/A 41202-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114940095</v>
+        <v>121667756</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>6648721</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,12 +881,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114940099</v>
+        <v>121667759</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
+        <v>97064</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>6648803</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,12 +988,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114940025</v>
+        <v>121667684</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>6648767</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114940026</v>
+        <v>121667685</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>6648811</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114940098</v>
+        <v>121667758</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>6648756</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114940097</v>
+        <v>121667757</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>6648744</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114940027</v>
+        <v>121667686</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>6648789</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114940024</v>
+        <v>121667683</v>
       </c>
       <c r="B10" t="n">
-        <v>78541</v>
+        <v>78648</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>6648739</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114940100</v>
+        <v>121667760</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
+        <v>98110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>6648820</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 41202-2024 artfynd.xlsx
+++ b/artfynd/A 41202-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>121667756</v>
       </c>
       <c r="B3" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>121667759</v>
       </c>
       <c r="B4" t="n">
-        <v>97064</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>121667684</v>
       </c>
       <c r="B5" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>121667685</v>
       </c>
       <c r="B6" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>121667758</v>
       </c>
       <c r="B7" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>121667757</v>
       </c>
       <c r="B8" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>121667686</v>
       </c>
       <c r="B9" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>121667683</v>
       </c>
       <c r="B10" t="n">
-        <v>78648</v>
+        <v>78650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>121667760</v>
       </c>
       <c r="B11" t="n">
-        <v>98110</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 41202-2024 artfynd.xlsx
+++ b/artfynd/A 41202-2024 artfynd.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 41202-2024 artfynd.xlsx
+++ b/artfynd/A 41202-2024 artfynd.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 41202-2024 artfynd.xlsx
+++ b/artfynd/A 41202-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>121667756</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>121667759</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>97085</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>121667684</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         <v>121667685</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
         <v>121667758</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>121667757</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>121667686</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1563,7 +1563,7 @@
         <v>121667683</v>
       </c>
       <c r="B10" t="n">
-        <v>78650</v>
+        <v>78663</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
         <v>121667760</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 41202-2024 artfynd.xlsx
+++ b/artfynd/A 41202-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>121667756</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>121667759</v>
       </c>
       <c r="B4" t="n">
-        <v>97085</v>
+        <v>97087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>121667684</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>121667685</v>
       </c>
       <c r="B6" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>121667758</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>121667757</v>
       </c>
       <c r="B8" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>121667686</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>121667683</v>
       </c>
       <c r="B10" t="n">
-        <v>78663</v>
+        <v>78665</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>121667760</v>
       </c>
       <c r="B11" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 41202-2024 artfynd.xlsx
+++ b/artfynd/A 41202-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>121667756</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>121667759</v>
       </c>
       <c r="B4" t="n">
-        <v>97087</v>
+        <v>97094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>121667684</v>
       </c>
       <c r="B5" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>121667685</v>
       </c>
       <c r="B6" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>121667758</v>
       </c>
       <c r="B7" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>121667757</v>
       </c>
       <c r="B8" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>121667686</v>
       </c>
       <c r="B9" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         <v>121667683</v>
       </c>
       <c r="B10" t="n">
-        <v>78665</v>
+        <v>78666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>121667760</v>
       </c>
       <c r="B11" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
